--- a/data/incc_report_input.xlsx
+++ b/data/incc_report_input.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8D4E77CE-6E4D-4589-9CC0-FA47171A91BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\otavi\Dropbox\jmp_inflation_rct\inflation_report\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57A64B89-B0F3-4B2C-B574-34C991CA20D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="incc" sheetId="1" r:id="rId1"/>
@@ -54,7 +59,7 @@
     <numFmt numFmtId="164" formatCode="mmmm/yyyy"/>
     <numFmt numFmtId="165" formatCode="#,##0.000"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -711,9 +716,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -751,7 +756,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -857,7 +862,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -999,7 +1004,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1007,14 +1012,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E221"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:E222"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1031,7 +1036,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>39448</v>
       </c>
@@ -1048,7 +1053,7 @@
         <v>6.08</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>39479</v>
       </c>
@@ -1065,7 +1070,7 @@
         <v>6.28</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>39508</v>
       </c>
@@ -1082,7 +1087,7 @@
         <v>6.69</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>39539</v>
       </c>
@@ -1099,7 +1104,7 @@
         <v>7.13</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>39569</v>
       </c>
@@ -1116,7 +1121,7 @@
         <v>8.06</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>39600</v>
       </c>
@@ -1133,7 +1138,7 @@
         <v>9.1300000000000008</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>39630</v>
       </c>
@@ -1150,7 +1155,7 @@
         <v>10.38</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>39661</v>
       </c>
@@ -1167,7 +1172,7 @@
         <v>11.4</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>39692</v>
       </c>
@@ -1184,7 +1189,7 @@
         <v>11.88</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>39722</v>
       </c>
@@ -1201,7 +1206,7 @@
         <v>12.18</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>39753</v>
       </c>
@@ -1218,7 +1223,7 @@
         <v>12.34</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="9">
         <v>39783</v>
       </c>
@@ -1235,7 +1240,7 @@
         <v>11.87</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>39814</v>
       </c>
@@ -1252,7 +1257,7 @@
         <v>11.82</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>39845</v>
       </c>
@@ -1269,7 +1274,7 @@
         <v>11.67</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <v>39873</v>
       </c>
@@ -1286,7 +1291,7 @@
         <v>10.66</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>39904</v>
       </c>
@@ -1303,7 +1308,7 @@
         <v>9.65</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <v>39934</v>
       </c>
@@ -1320,7 +1325,7 @@
         <v>8.98</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>39965</v>
       </c>
@@ -1337,7 +1342,7 @@
         <v>7.67</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
         <v>39995</v>
       </c>
@@ -1354,7 +1359,7 @@
         <v>6.4</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>40026</v>
       </c>
@@ -1371,7 +1376,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <v>40057</v>
       </c>
@@ -1388,7 +1393,7 @@
         <v>4.2699999999999996</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>40087</v>
       </c>
@@ -1405,7 +1410,7 @@
         <v>3.53</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
         <v>40118</v>
       </c>
@@ -1422,7 +1427,7 @@
         <v>3.32</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="9">
         <v>40148</v>
       </c>
@@ -1439,7 +1444,7 @@
         <v>3.25</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>40179</v>
       </c>
@@ -1456,7 +1461,7 @@
         <v>3.56</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <v>40210</v>
       </c>
@@ -1473,7 +1478,7 @@
         <v>3.66</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
         <v>40238</v>
       </c>
@@ -1490,7 +1495,7 @@
         <v>4.71</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <v>40269</v>
       </c>
@@ -1507,7 +1512,7 @@
         <v>5.63</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
         <v>40299</v>
       </c>
@@ -1524,7 +1529,7 @@
         <v>6.07</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
         <v>40330</v>
       </c>
@@ -1541,7 +1546,7 @@
         <v>6.48</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
         <v>40360</v>
       </c>
@@ -1558,7 +1563,7 @@
         <v>6.67</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
         <v>40391</v>
       </c>
@@ -1575,7 +1580,7 @@
         <v>6.87</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
         <v>40422</v>
       </c>
@@ -1592,7 +1597,7 @@
         <v>6.94</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
         <v>40452</v>
       </c>
@@ -1609,7 +1614,7 @@
         <v>7.08</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
         <v>40483</v>
       </c>
@@ -1626,7 +1631,7 @@
         <v>7.16</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="9">
         <v>40513</v>
       </c>
@@ -1643,7 +1648,7 @@
         <v>7.77</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>40544</v>
       </c>
@@ -1660,7 +1665,7 @@
         <v>7.52</v>
       </c>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
         <v>40575</v>
       </c>
@@ -1677,7 +1682,7 @@
         <v>7.44</v>
       </c>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
         <v>40603</v>
       </c>
@@ -1694,7 +1699,7 @@
         <v>7.1</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="5">
         <v>40634</v>
       </c>
@@ -1711,7 +1716,7 @@
         <v>7.33</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="13">
         <v>40664</v>
       </c>
@@ -1728,7 +1733,7 @@
         <v>8.52</v>
       </c>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="13">
         <v>40695</v>
       </c>
@@ -1745,7 +1750,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="13">
         <v>40726</v>
       </c>
@@ -1762,7 +1767,7 @@
         <v>7.76</v>
       </c>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="13">
         <v>40756</v>
       </c>
@@ -1779,7 +1784,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="13">
         <v>40787</v>
       </c>
@@ -1796,7 +1801,7 @@
         <v>7.68</v>
       </c>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="13">
         <v>40817</v>
       </c>
@@ -1813,7 +1818,7 @@
         <v>7.72</v>
       </c>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="13">
         <v>40848</v>
       </c>
@@ -1830,7 +1835,7 @@
         <v>8.09</v>
       </c>
     </row>
-    <row r="49" spans="1:5">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="9">
         <v>40878</v>
       </c>
@@ -1847,7 +1852,7 @@
         <v>7.49</v>
       </c>
     </row>
-    <row r="50" spans="1:5">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="19">
         <v>40909</v>
       </c>
@@ -1864,7 +1869,7 @@
         <v>8.01</v>
       </c>
     </row>
-    <row r="51" spans="1:5">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="13">
         <v>40940</v>
       </c>
@@ -1881,7 +1886,7 @@
         <v>8.02</v>
       </c>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="13">
         <v>40969</v>
       </c>
@@ -1898,7 +1903,7 @@
         <v>8.1</v>
       </c>
     </row>
-    <row r="53" spans="1:5">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="13">
         <v>41000</v>
       </c>
@@ -1915,7 +1920,7 @@
         <v>7.77</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="13">
         <v>41030</v>
       </c>
@@ -1932,7 +1937,7 @@
         <v>6.66</v>
       </c>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="13">
         <v>41061</v>
       </c>
@@ -1949,7 +1954,7 @@
         <v>7.04</v>
       </c>
     </row>
-    <row r="56" spans="1:5">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="13">
         <v>41091</v>
       </c>
@@ -1966,7 +1971,7 @@
         <v>7.27</v>
       </c>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="13">
         <v>41122</v>
       </c>
@@ -1983,7 +1988,7 @@
         <v>7.41</v>
       </c>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="13">
         <v>41153</v>
       </c>
@@ -2000,7 +2005,7 @@
         <v>7.49</v>
       </c>
     </row>
-    <row r="59" spans="1:5">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="13">
         <v>41183</v>
       </c>
@@ -2017,7 +2022,7 @@
         <v>7.47</v>
       </c>
     </row>
-    <row r="60" spans="1:5">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="13">
         <v>41214</v>
       </c>
@@ -2034,7 +2039,7 @@
         <v>7.06</v>
       </c>
     </row>
-    <row r="61" spans="1:5">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="9">
         <v>41244</v>
       </c>
@@ -2051,7 +2056,7 @@
         <v>7.12</v>
       </c>
     </row>
-    <row r="62" spans="1:5">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>41275</v>
       </c>
@@ -2068,7 +2073,7 @@
         <v>6.86</v>
       </c>
     </row>
-    <row r="63" spans="1:5">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="13">
         <v>41306</v>
       </c>
@@ -2085,7 +2090,7 @@
         <v>7.18</v>
       </c>
     </row>
-    <row r="64" spans="1:5">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="13">
         <v>41334</v>
       </c>
@@ -2102,7 +2107,7 @@
         <v>7.18</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="13">
         <v>41365</v>
       </c>
@@ -2119,7 +2124,7 @@
         <v>7.16</v>
       </c>
     </row>
-    <row r="66" spans="1:5">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="13">
         <v>41395</v>
       </c>
@@ -2136,7 +2141,7 @@
         <v>7.56</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="13">
         <v>41426</v>
       </c>
@@ -2153,7 +2158,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="13">
         <v>41456</v>
       </c>
@@ -2170,7 +2175,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="69" spans="1:5">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="13">
         <v>41487</v>
       </c>
@@ -2187,7 +2192,7 @@
         <v>7.86</v>
       </c>
     </row>
-    <row r="70" spans="1:5">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="13">
         <v>41518</v>
       </c>
@@ -2204,7 +2209,7 @@
         <v>8.09</v>
       </c>
     </row>
-    <row r="71" spans="1:5">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="13">
         <v>41548</v>
       </c>
@@ -2221,7 +2226,7 @@
         <v>8.14</v>
       </c>
     </row>
-    <row r="72" spans="1:5">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="13">
         <v>41579</v>
       </c>
@@ -2238,7 +2243,7 @@
         <v>8.16</v>
       </c>
     </row>
-    <row r="73" spans="1:5">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="9">
         <v>41609</v>
       </c>
@@ -2255,7 +2260,7 @@
         <v>8.09</v>
       </c>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="13">
         <v>41640</v>
       </c>
@@ -2272,7 +2277,7 @@
         <v>8.34</v>
       </c>
     </row>
-    <row r="75" spans="1:5">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="13">
         <v>41671</v>
       </c>
@@ -2289,7 +2294,7 @@
         <v>8.0399999999999991</v>
       </c>
     </row>
-    <row r="76" spans="1:5">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="13">
         <v>41699</v>
       </c>
@@ -2306,7 +2311,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="77" spans="1:5">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="13">
         <v>41730</v>
       </c>
@@ -2323,7 +2328,7 @@
         <v>7.96</v>
       </c>
     </row>
-    <row r="78" spans="1:5">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="13">
         <v>41760</v>
       </c>
@@ -2340,7 +2345,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="79" spans="1:5">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="13">
         <v>41791</v>
       </c>
@@ -2357,7 +2362,7 @@
         <v>7.23</v>
       </c>
     </row>
-    <row r="80" spans="1:5">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="13">
         <v>41821</v>
       </c>
@@ -2374,7 +2379,7 @@
         <v>7.52</v>
       </c>
     </row>
-    <row r="81" spans="1:5">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="13">
         <v>41852</v>
       </c>
@@ -2391,7 +2396,7 @@
         <v>7.26</v>
       </c>
     </row>
-    <row r="82" spans="1:5">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="13">
         <v>41883</v>
       </c>
@@ -2408,7 +2413,7 @@
         <v>6.96</v>
       </c>
     </row>
-    <row r="83" spans="1:5">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="13">
         <v>41913</v>
       </c>
@@ -2425,7 +2430,7 @@
         <v>6.87</v>
       </c>
     </row>
-    <row r="84" spans="1:5">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="13">
         <v>41944</v>
       </c>
@@ -2442,7 +2447,7 @@
         <v>6.97</v>
       </c>
     </row>
-    <row r="85" spans="1:5">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="9">
         <v>41974</v>
       </c>
@@ -2459,7 +2464,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="86" spans="1:5">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="19">
         <v>42005</v>
       </c>
@@ -2476,7 +2481,7 @@
         <v>6.99</v>
       </c>
     </row>
-    <row r="87" spans="1:5">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="13">
         <v>42036</v>
       </c>
@@ -2493,7 +2498,7 @@
         <v>6.98</v>
       </c>
     </row>
-    <row r="88" spans="1:5">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="13">
         <v>42064</v>
       </c>
@@ -2510,7 +2515,7 @@
         <v>7.34</v>
       </c>
     </row>
-    <row r="89" spans="1:5">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="13">
         <v>42095</v>
       </c>
@@ -2527,7 +2532,7 @@
         <v>6.89</v>
       </c>
     </row>
-    <row r="90" spans="1:5">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="13">
         <v>42125</v>
       </c>
@@ -2544,7 +2549,7 @@
         <v>5.74</v>
       </c>
     </row>
-    <row r="91" spans="1:5">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="13">
         <v>42156</v>
       </c>
@@ -2561,7 +2566,7 @@
         <v>6.97</v>
       </c>
     </row>
-    <row r="92" spans="1:5">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="13">
         <v>42186</v>
       </c>
@@ -2578,7 +2583,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="93" spans="1:5">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="13">
         <v>42217</v>
       </c>
@@ -2595,7 +2600,7 @@
         <v>7.3</v>
       </c>
     </row>
-    <row r="94" spans="1:5">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="13">
         <v>42248</v>
       </c>
@@ -2612,7 +2617,7 @@
         <v>7.37</v>
       </c>
     </row>
-    <row r="95" spans="1:5">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="13">
         <v>42278</v>
       </c>
@@ -2629,7 +2634,7 @@
         <v>7.57</v>
       </c>
     </row>
-    <row r="96" spans="1:5">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="13">
         <v>42309</v>
       </c>
@@ -2646,7 +2651,7 @@
         <v>7.46</v>
       </c>
     </row>
-    <row r="97" spans="1:5">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="9">
         <v>42339</v>
       </c>
@@ -2663,7 +2668,7 @@
         <v>7.48</v>
       </c>
     </row>
-    <row r="98" spans="1:5">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="13">
         <v>42370</v>
       </c>
@@ -2680,7 +2685,7 @@
         <v>6.92</v>
       </c>
     </row>
-    <row r="99" spans="1:5">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="13">
         <v>42401</v>
       </c>
@@ -2697,7 +2702,7 @@
         <v>7.17</v>
       </c>
     </row>
-    <row r="100" spans="1:5">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="13">
         <v>42430</v>
       </c>
@@ -2714,7 +2719,7 @@
         <v>7.18</v>
       </c>
     </row>
-    <row r="101" spans="1:5">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="13">
         <v>42461</v>
       </c>
@@ -2731,7 +2736,7 @@
         <v>7.28</v>
       </c>
     </row>
-    <row r="102" spans="1:5">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="13">
         <v>42491</v>
       </c>
@@ -2748,7 +2753,7 @@
         <v>6.36</v>
       </c>
     </row>
-    <row r="103" spans="1:5">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="13">
         <v>42522</v>
       </c>
@@ -2765,7 +2770,7 @@
         <v>6.46</v>
       </c>
     </row>
-    <row r="104" spans="1:5">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="13">
         <v>42552</v>
       </c>
@@ -2782,7 +2787,7 @@
         <v>6.4</v>
       </c>
     </row>
-    <row r="105" spans="1:5">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="13">
         <v>42583</v>
       </c>
@@ -2799,7 +2804,7 @@
         <v>6.09</v>
       </c>
     </row>
-    <row r="106" spans="1:5">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="13">
         <v>42614</v>
       </c>
@@ -2816,7 +2821,7 @@
         <v>6.21</v>
       </c>
     </row>
-    <row r="107" spans="1:5">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="13">
         <v>42644</v>
       </c>
@@ -2833,7 +2838,7 @@
         <v>6.05</v>
       </c>
     </row>
-    <row r="108" spans="1:5">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="13">
         <v>42675</v>
       </c>
@@ -2850,7 +2855,7 @@
         <v>5.87</v>
       </c>
     </row>
-    <row r="109" spans="1:5">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="9">
         <v>42705</v>
       </c>
@@ -2867,7 +2872,7 @@
         <v>6.13</v>
       </c>
     </row>
-    <row r="110" spans="1:5">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="13">
         <v>42736</v>
       </c>
@@ -2884,7 +2889,7 @@
         <v>6.14</v>
       </c>
     </row>
-    <row r="111" spans="1:5">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="13">
         <v>42767</v>
       </c>
@@ -2901,7 +2906,7 @@
         <v>6.26</v>
       </c>
     </row>
-    <row r="112" spans="1:5">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="13">
         <v>42795</v>
       </c>
@@ -2918,7 +2923,7 @@
         <v>5.76</v>
       </c>
     </row>
-    <row r="113" spans="1:5">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="13">
         <v>42826</v>
       </c>
@@ -2935,7 +2940,7 @@
         <v>5.16</v>
       </c>
     </row>
-    <row r="114" spans="1:5">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="13">
         <v>42856</v>
       </c>
@@ -2952,7 +2957,7 @@
         <v>5.73</v>
       </c>
     </row>
-    <row r="115" spans="1:5">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="13">
         <v>42887</v>
       </c>
@@ -2969,7 +2974,7 @@
         <v>4.7</v>
       </c>
     </row>
-    <row r="116" spans="1:5">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="13">
         <v>42917</v>
       </c>
@@ -2986,7 +2991,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="117" spans="1:5">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="13">
         <v>42948</v>
       </c>
@@ -3003,7 +3008,7 @@
         <v>4.57</v>
       </c>
     </row>
-    <row r="118" spans="1:5">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="13">
         <v>42979</v>
       </c>
@@ -3020,7 +3025,7 @@
         <v>4.28</v>
       </c>
     </row>
-    <row r="119" spans="1:5">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="13">
         <v>43009</v>
       </c>
@@ -3037,7 +3042,7 @@
         <v>4.38</v>
       </c>
     </row>
-    <row r="120" spans="1:5">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="13">
         <v>43040</v>
       </c>
@@ -3054,7 +3059,7 @@
         <v>4.54</v>
       </c>
     </row>
-    <row r="121" spans="1:5">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="9">
         <v>43070</v>
       </c>
@@ -3071,7 +3076,7 @@
         <v>4.25</v>
       </c>
     </row>
-    <row r="122" spans="1:5">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>43101</v>
       </c>
@@ -3088,7 +3093,7 @@
         <v>4.1500000000000004</v>
       </c>
     </row>
-    <row r="123" spans="1:5">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="5">
         <v>43132</v>
       </c>
@@ -3105,7 +3110,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="124" spans="1:5">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="5">
         <v>43160</v>
       </c>
@@ -3122,7 +3127,7 @@
         <v>3.69</v>
       </c>
     </row>
-    <row r="125" spans="1:5">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="5">
         <v>43191</v>
       </c>
@@ -3139,7 +3144,7 @@
         <v>4.0199999999999996</v>
       </c>
     </row>
-    <row r="126" spans="1:5">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="5">
         <v>43221</v>
       </c>
@@ -3156,7 +3161,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="127" spans="1:5">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="5">
         <v>43252</v>
       </c>
@@ -3173,7 +3178,7 @@
         <v>3.64</v>
       </c>
     </row>
-    <row r="128" spans="1:5">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="13">
         <v>43282</v>
       </c>
@@ -3190,7 +3195,7 @@
         <v>3.96</v>
       </c>
     </row>
-    <row r="129" spans="1:5">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="13">
         <v>43313</v>
       </c>
@@ -3207,7 +3212,7 @@
         <v>3.75</v>
       </c>
     </row>
-    <row r="130" spans="1:5">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="13">
         <v>43344</v>
       </c>
@@ -3224,7 +3229,7 @@
         <v>3.92</v>
       </c>
     </row>
-    <row r="131" spans="1:5">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" s="13">
         <v>43374</v>
       </c>
@@ -3241,7 +3246,7 @@
         <v>3.96</v>
       </c>
     </row>
-    <row r="132" spans="1:5">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="13">
         <v>43405</v>
       </c>
@@ -3258,7 +3263,7 @@
         <v>3.78</v>
       </c>
     </row>
-    <row r="133" spans="1:5">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" s="9">
         <v>43435</v>
       </c>
@@ -3275,7 +3280,7 @@
         <v>3.84</v>
       </c>
     </row>
-    <row r="134" spans="1:5">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="19">
         <v>43466</v>
       </c>
@@ -3292,7 +3297,7 @@
         <v>4.03</v>
       </c>
     </row>
-    <row r="135" spans="1:5">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="13">
         <v>43497</v>
       </c>
@@ -3309,7 +3314,7 @@
         <v>3.99</v>
       </c>
     </row>
-    <row r="136" spans="1:5">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" s="13">
         <v>43525</v>
       </c>
@@ -3326,7 +3331,7 @@
         <v>4.0599999999999996</v>
       </c>
     </row>
-    <row r="137" spans="1:5">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" s="13">
         <v>43556</v>
       </c>
@@ -3343,7 +3348,7 @@
         <v>4.1500000000000004</v>
       </c>
     </row>
-    <row r="138" spans="1:5">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" s="13">
         <v>43586</v>
       </c>
@@ -3360,7 +3365,7 @@
         <v>3.95</v>
       </c>
     </row>
-    <row r="139" spans="1:5">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" s="13">
         <v>43617</v>
       </c>
@@ -3377,7 +3382,7 @@
         <v>3.86</v>
       </c>
     </row>
-    <row r="140" spans="1:5">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" s="13">
         <v>43647</v>
       </c>
@@ -3394,7 +3399,7 @@
         <v>3.82</v>
       </c>
     </row>
-    <row r="141" spans="1:5">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" s="13">
         <v>43678</v>
       </c>
@@ -3411,7 +3416,7 @@
         <v>4.1100000000000003</v>
       </c>
     </row>
-    <row r="142" spans="1:5">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" s="13">
         <v>43709</v>
       </c>
@@ -3428,7 +3433,7 @@
         <v>4.3499999999999996</v>
       </c>
     </row>
-    <row r="143" spans="1:5">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" s="13">
         <v>43739</v>
       </c>
@@ -3445,7 +3450,7 @@
         <v>4.18</v>
       </c>
     </row>
-    <row r="144" spans="1:5">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" s="13">
         <v>43770</v>
       </c>
@@ -3462,7 +3467,7 @@
         <v>4.08</v>
       </c>
     </row>
-    <row r="145" spans="1:5">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" s="9">
         <v>43800</v>
       </c>
@@ -3479,7 +3484,7 @@
         <v>4.1500000000000004</v>
       </c>
     </row>
-    <row r="146" spans="1:5">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" s="19">
         <v>43831</v>
       </c>
@@ -3496,7 +3501,7 @@
         <v>4.04</v>
       </c>
     </row>
-    <row r="147" spans="1:5">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" s="13">
         <v>43862</v>
       </c>
@@ -3513,7 +3518,7 @@
         <v>4.29</v>
       </c>
     </row>
-    <row r="148" spans="1:5">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" s="13">
         <v>43891</v>
       </c>
@@ -3530,7 +3535,7 @@
         <v>4.2300000000000004</v>
       </c>
     </row>
-    <row r="149" spans="1:5">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" s="13">
         <v>43922</v>
       </c>
@@ -3547,7 +3552,7 @@
         <v>4.0599999999999996</v>
       </c>
     </row>
-    <row r="150" spans="1:5">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" s="13">
         <v>43952</v>
       </c>
@@ -3564,7 +3569,7 @@
         <v>4.24</v>
       </c>
     </row>
-    <row r="151" spans="1:5">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" s="13">
         <v>43983</v>
       </c>
@@ -3581,7 +3586,7 @@
         <v>3.68</v>
       </c>
     </row>
-    <row r="152" spans="1:5">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" s="13">
         <v>44013</v>
       </c>
@@ -3598,7 +3603,7 @@
         <v>4.29</v>
       </c>
     </row>
-    <row r="153" spans="1:5">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" s="13">
         <v>44044</v>
       </c>
@@ -3615,7 +3620,7 @@
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="154" spans="1:5">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" s="13">
         <v>44075</v>
       </c>
@@ -3632,7 +3637,7 @@
         <v>5.32</v>
       </c>
     </row>
-    <row r="155" spans="1:5">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" s="13">
         <v>44105</v>
       </c>
@@ -3649,7 +3654,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="156" spans="1:5">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" s="13">
         <v>44136</v>
       </c>
@@ -3666,7 +3671,7 @@
         <v>8.2799999999999994</v>
       </c>
     </row>
-    <row r="157" spans="1:5">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" s="9">
         <v>44166</v>
       </c>
@@ -3683,7 +3688,7 @@
         <v>8.81</v>
       </c>
     </row>
-    <row r="158" spans="1:5">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" s="13">
         <v>44197</v>
       </c>
@@ -3700,7 +3705,7 @@
         <v>9.3699999999999992</v>
       </c>
     </row>
-    <row r="159" spans="1:5">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" s="13">
         <v>44228</v>
       </c>
@@ -3717,7 +3722,7 @@
         <v>11.07</v>
       </c>
     </row>
-    <row r="160" spans="1:5">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" s="23">
         <v>44256</v>
       </c>
@@ -3734,7 +3739,7 @@
         <v>12.23</v>
       </c>
     </row>
-    <row r="161" spans="1:5">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" s="13">
         <v>44287</v>
       </c>
@@ -3751,7 +3756,7 @@
         <v>12.99</v>
       </c>
     </row>
-    <row r="162" spans="1:5">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" s="13">
         <v>44317</v>
       </c>
@@ -3768,7 +3773,7 @@
         <v>15.26</v>
       </c>
     </row>
-    <row r="163" spans="1:5">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" s="13">
         <v>44348</v>
       </c>
@@ -3785,7 +3790,7 @@
         <v>17.36</v>
       </c>
     </row>
-    <row r="164" spans="1:5">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" s="13">
         <v>44378</v>
       </c>
@@ -3802,7 +3807,7 @@
         <v>16.98</v>
       </c>
     </row>
-    <row r="165" spans="1:5">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" s="13">
         <v>44409</v>
       </c>
@@ -3819,7 +3824,7 @@
         <v>16.68</v>
       </c>
     </row>
-    <row r="166" spans="1:5">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" s="13">
         <v>44440</v>
       </c>
@@ -3836,7 +3841,7 @@
         <v>15.93</v>
       </c>
     </row>
-    <row r="167" spans="1:5">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" s="13">
         <v>44470</v>
       </c>
@@ -3853,7 +3858,7 @@
         <v>14.94</v>
       </c>
     </row>
-    <row r="168" spans="1:5">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" s="13">
         <v>44501</v>
       </c>
@@ -3870,7 +3875,7 @@
         <v>14.25</v>
       </c>
     </row>
-    <row r="169" spans="1:5">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" s="9">
         <v>44531</v>
       </c>
@@ -3887,7 +3892,7 @@
         <v>13.85</v>
       </c>
     </row>
-    <row r="170" spans="1:5">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" s="13">
         <v>44562</v>
       </c>
@@ -3904,7 +3909,7 @@
         <v>13.65</v>
       </c>
     </row>
-    <row r="171" spans="1:5">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" s="13">
         <v>44593</v>
       </c>
@@ -3921,7 +3926,7 @@
         <v>11.97</v>
       </c>
     </row>
-    <row r="172" spans="1:5">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" s="13">
         <v>44621</v>
       </c>
@@ -3938,7 +3943,7 @@
         <v>11.47</v>
       </c>
     </row>
-    <row r="173" spans="1:5">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" s="13">
         <v>44652</v>
       </c>
@@ -3955,7 +3960,7 @@
         <v>11.52</v>
       </c>
     </row>
-    <row r="174" spans="1:5">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" s="13">
         <v>44682</v>
       </c>
@@ -3972,7 +3977,7 @@
         <v>11.59</v>
       </c>
     </row>
-    <row r="175" spans="1:5">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" s="13">
         <v>44713</v>
       </c>
@@ -3989,7 +3994,7 @@
         <v>11.57</v>
       </c>
     </row>
-    <row r="176" spans="1:5">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" s="13">
         <v>44743</v>
       </c>
@@ -4006,7 +4011,7 @@
         <v>11.59</v>
       </c>
     </row>
-    <row r="177" spans="1:5">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" s="13">
         <v>44774</v>
       </c>
@@ -4023,7 +4028,7 @@
         <v>11.17</v>
       </c>
     </row>
-    <row r="178" spans="1:5">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" s="13">
         <v>44805</v>
       </c>
@@ -4040,7 +4045,7 @@
         <v>10.7</v>
       </c>
     </row>
-    <row r="179" spans="1:5">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" s="13">
         <v>44835</v>
       </c>
@@ -4057,7 +4062,7 @@
         <v>9.9</v>
       </c>
     </row>
-    <row r="180" spans="1:5">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" s="13">
         <v>44866</v>
       </c>
@@ -4074,7 +4079,7 @@
         <v>9.56</v>
       </c>
     </row>
-    <row r="181" spans="1:5">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" s="9">
         <v>44896</v>
       </c>
@@ -4091,7 +4096,7 @@
         <v>9.2799999999999994</v>
       </c>
     </row>
-    <row r="182" spans="1:5">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" s="13">
         <v>44927</v>
       </c>
@@ -4108,7 +4113,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="183" spans="1:5">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" s="13">
         <v>44958</v>
       </c>
@@ -4125,7 +4130,7 @@
         <v>8.6300000000000008</v>
       </c>
     </row>
-    <row r="184" spans="1:5">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" s="13">
         <v>44986</v>
       </c>
@@ -4142,7 +4147,7 @@
         <v>8.0399999999999991</v>
       </c>
     </row>
-    <row r="185" spans="1:5">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" s="13">
         <v>45017</v>
       </c>
@@ -4159,7 +4164,7 @@
         <v>7.18</v>
       </c>
     </row>
-    <row r="186" spans="1:5">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" s="13">
         <v>45047</v>
       </c>
@@ -4176,7 +4181,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="187" spans="1:5">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" s="13">
         <v>45078</v>
       </c>
@@ -4193,7 +4198,7 @@
         <v>3.93</v>
       </c>
     </row>
-    <row r="188" spans="1:5">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" s="13">
         <v>45108</v>
       </c>
@@ -4210,7 +4215,7 @@
         <v>3.15</v>
       </c>
     </row>
-    <row r="189" spans="1:5">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" s="13">
         <v>45139</v>
       </c>
@@ -4227,7 +4232,7 @@
         <v>3.23</v>
       </c>
     </row>
-    <row r="190" spans="1:5">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" s="13">
         <v>45170</v>
       </c>
@@ -4244,7 +4249,7 @@
         <v>3.49</v>
       </c>
     </row>
-    <row r="191" spans="1:5">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" s="13">
         <v>45200</v>
       </c>
@@ -4261,7 +4266,7 @@
         <v>3.57</v>
       </c>
     </row>
-    <row r="192" spans="1:5">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" s="13">
         <v>45231</v>
       </c>
@@ -4278,7 +4283,7 @@
         <v>3.26</v>
       </c>
     </row>
-    <row r="193" spans="1:5">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" s="13">
         <v>45261</v>
       </c>
@@ -4295,7 +4300,7 @@
         <v>3.49</v>
       </c>
     </row>
-    <row r="194" spans="1:5">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" s="19">
         <v>45292</v>
       </c>
@@ -4312,7 +4317,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="195" spans="1:5">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" s="13">
         <v>45323</v>
       </c>
@@ -4329,7 +4334,7 @@
         <v>3.39</v>
       </c>
     </row>
-    <row r="196" spans="1:5">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" s="13">
         <v>45352</v>
       </c>
@@ -4346,7 +4351,7 @@
         <v>3.36</v>
       </c>
     </row>
-    <row r="197" spans="1:5">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197" s="13">
         <v>45383</v>
       </c>
@@ -4363,7 +4368,7 @@
         <v>3.74</v>
       </c>
     </row>
-    <row r="198" spans="1:5">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" s="13">
         <v>45413</v>
       </c>
@@ -4380,7 +4385,7 @@
         <v>4.0199999999999996</v>
       </c>
     </row>
-    <row r="199" spans="1:5">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A199" s="13">
         <v>45444</v>
       </c>
@@ -4397,7 +4402,7 @@
         <v>4.0199999999999996</v>
       </c>
     </row>
-    <row r="200" spans="1:5">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200" s="13">
         <v>45474</v>
       </c>
@@ -4414,7 +4419,7 @@
         <v>4.67</v>
       </c>
     </row>
-    <row r="201" spans="1:5">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201" s="23">
         <v>45505</v>
       </c>
@@ -4431,7 +4436,7 @@
         <v>5.23</v>
       </c>
     </row>
-    <row r="202" spans="1:5">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A202" s="23">
         <v>45536</v>
       </c>
@@ -4448,7 +4453,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="203" spans="1:5">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A203" s="23">
         <v>45566</v>
       </c>
@@ -4465,7 +4470,7 @@
         <v>5.99</v>
       </c>
     </row>
-    <row r="204" spans="1:5">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A204" s="13">
         <v>45597</v>
       </c>
@@ -4482,7 +4487,7 @@
         <v>6.34</v>
       </c>
     </row>
-    <row r="205" spans="1:5">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A205" s="27">
         <v>45627</v>
       </c>
@@ -4499,7 +4504,7 @@
         <v>6.54</v>
       </c>
     </row>
-    <row r="206" spans="1:5">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A206" s="19">
         <v>45658</v>
       </c>
@@ -4516,7 +4521,7 @@
         <v>7.14</v>
       </c>
     </row>
-    <row r="207" spans="1:5">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A207" s="31">
         <v>45689</v>
       </c>
@@ -4533,7 +4538,7 @@
         <v>7.42</v>
       </c>
     </row>
-    <row r="208" spans="1:5">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A208" s="31">
         <v>45717</v>
       </c>
@@ -4550,7 +4555,7 @@
         <v>7.54</v>
       </c>
     </row>
-    <row r="209" spans="1:5">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A209" s="31">
         <v>45748</v>
       </c>
@@ -4567,7 +4572,7 @@
         <v>7.54</v>
       </c>
     </row>
-    <row r="210" spans="1:5">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A210" s="31">
         <v>45778</v>
       </c>
@@ -4584,7 +4589,7 @@
         <v>7.24</v>
       </c>
     </row>
-    <row r="211" spans="1:5">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A211" s="23">
         <v>45809</v>
       </c>
@@ -4601,7 +4606,7 @@
         <v>7.21</v>
       </c>
     </row>
-    <row r="212" spans="1:5">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A212" s="23">
         <v>45839</v>
       </c>
@@ -4618,7 +4623,7 @@
         <v>7.41</v>
       </c>
     </row>
-    <row r="213" spans="1:5">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213" s="23">
         <v>45870</v>
       </c>
@@ -4635,7 +4640,7 @@
         <v>7.22</v>
       </c>
     </row>
-    <row r="214" spans="1:5">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A214" s="23">
         <v>45901</v>
       </c>
@@ -4652,7 +4657,7 @@
         <v>6.78</v>
       </c>
     </row>
-    <row r="215" spans="1:5">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A215" s="23">
         <v>45931</v>
       </c>
@@ -4669,7 +4674,7 @@
         <v>6.37</v>
       </c>
     </row>
-    <row r="216" spans="1:5">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A216" s="23">
         <v>45962</v>
       </c>
@@ -4686,7 +4691,7 @@
         <v>6.23</v>
       </c>
     </row>
-    <row r="217" spans="1:5">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A217" s="27">
         <v>45992</v>
       </c>
@@ -4703,7 +4708,7 @@
         <v>5.92</v>
       </c>
     </row>
-    <row r="218" spans="1:5">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A218" s="23">
         <v>46023</v>
       </c>
@@ -4720,7 +4725,7 @@
         <v>5.81</v>
       </c>
     </row>
-    <row r="219" spans="1:5">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A219" s="13">
         <v>46054</v>
       </c>
@@ -4737,7 +4742,7 @@
         <v>5.68</v>
       </c>
     </row>
-    <row r="220" spans="1:5">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A220" s="27">
         <v>46082</v>
       </c>
@@ -4754,7 +4759,7 @@
         <v>5.84</v>
       </c>
     </row>
-    <row r="221" spans="1:5">
+    <row r="221" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A221" s="35">
         <v>46113</v>
       </c>
@@ -4769,6 +4774,23 @@
       </c>
       <c r="E221" s="37">
         <v>6.35</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A222" s="23">
+        <v>46143</v>
+      </c>
+      <c r="B222" s="28">
+        <v>1270.6949999999999</v>
+      </c>
+      <c r="C222" s="25">
+        <v>0.88</v>
+      </c>
+      <c r="D222" s="25">
+        <v>3.46</v>
+      </c>
+      <c r="E222" s="26">
+        <v>6.66</v>
       </c>
     </row>
   </sheetData>
@@ -4778,8 +4800,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73776E25-10CF-4014-99F4-95DB4E70373B}">
-  <dimension ref="A1:E221"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:E222"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.28515625" customWidth="1"/>
@@ -4787,7 +4809,7 @@
     <col min="5" max="5" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4804,7 +4826,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>39448</v>
       </c>
@@ -4821,7 +4843,7 @@
         <v>4.5599999999999996</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>39479</v>
       </c>
@@ -4838,7 +4860,7 @@
         <v>4.6100000000000003</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>39508</v>
       </c>
@@ -4855,7 +4877,7 @@
         <v>4.7300000000000004</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>39539</v>
       </c>
@@ -4872,7 +4894,7 @@
         <v>5.04</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>39569</v>
       </c>
@@ -4889,7 +4911,7 @@
         <v>5.58</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>39600</v>
       </c>
@@ -4906,7 +4928,7 @@
         <v>6.06</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>39630</v>
       </c>
@@ -4923,7 +4945,7 @@
         <v>6.37</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>39661</v>
       </c>
@@ -4940,7 +4962,7 @@
         <v>6.17</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>39692</v>
       </c>
@@ -4957,7 +4979,7 @@
         <v>6.25</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>39722</v>
       </c>
@@ -4974,7 +4996,7 @@
         <v>6.41</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>39753</v>
       </c>
@@ -4991,7 +5013,7 @@
         <v>6.39</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="9">
         <v>39783</v>
       </c>
@@ -5008,7 +5030,7 @@
         <v>5.9</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>39814</v>
       </c>
@@ -5025,7 +5047,7 @@
         <v>5.84</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>39845</v>
       </c>
@@ -5042,7 +5064,7 @@
         <v>5.9</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <v>39873</v>
       </c>
@@ -5059,7 +5081,7 @@
         <v>5.61</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>39904</v>
       </c>
@@ -5076,7 +5098,7 @@
         <v>5.53</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <v>39934</v>
       </c>
@@ -5093,7 +5115,7 @@
         <v>5.2</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>39965</v>
       </c>
@@ -5110,7 +5132,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
         <v>39995</v>
       </c>
@@ -5127,7 +5149,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>40026</v>
       </c>
@@ -5144,7 +5166,7 @@
         <v>4.3600000000000003</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <v>40057</v>
       </c>
@@ -5161,7 +5183,7 @@
         <v>4.34</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>40087</v>
       </c>
@@ -5178,7 +5200,7 @@
         <v>4.17</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
         <v>40118</v>
       </c>
@@ -5195,7 +5217,7 @@
         <v>4.22</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="9">
         <v>40148</v>
       </c>
@@ -5212,7 +5234,7 @@
         <v>4.3099999999999996</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>40179</v>
       </c>
@@ -5229,7 +5251,7 @@
         <v>4.59</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <v>40210</v>
       </c>
@@ -5246,7 +5268,7 @@
         <v>4.83</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
         <v>40238</v>
       </c>
@@ -5263,7 +5285,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <v>40269</v>
       </c>
@@ -5280,7 +5302,7 @@
         <v>5.26</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
         <v>40299</v>
       </c>
@@ -5297,7 +5319,7 @@
         <v>5.22</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
         <v>40330</v>
       </c>
@@ -5314,7 +5336,7 @@
         <v>4.84</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
         <v>40360</v>
       </c>
@@ -5331,7 +5353,7 @@
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
         <v>40391</v>
       </c>
@@ -5348,7 +5370,7 @@
         <v>4.49</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
         <v>40422</v>
       </c>
@@ -5365,7 +5387,7 @@
         <v>4.7</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
         <v>40452</v>
       </c>
@@ -5382,7 +5404,7 @@
         <v>5.2</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
         <v>40483</v>
       </c>
@@ -5399,7 +5421,7 @@
         <v>5.63</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="9">
         <v>40513</v>
       </c>
@@ -5416,7 +5438,7 @@
         <v>5.91</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>40544</v>
       </c>
@@ -5433,7 +5455,7 @@
         <v>5.99</v>
       </c>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
         <v>40575</v>
       </c>
@@ -5450,7 +5472,7 @@
         <v>6.01</v>
       </c>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
         <v>40603</v>
       </c>
@@ -5467,7 +5489,7 @@
         <v>6.3</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="5">
         <v>40634</v>
       </c>
@@ -5484,7 +5506,7 @@
         <v>6.51</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="5">
         <v>40664</v>
       </c>
@@ -5501,7 +5523,7 @@
         <v>6.55</v>
       </c>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="13">
         <v>40695</v>
       </c>
@@ -5518,7 +5540,7 @@
         <v>6.71</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="13">
         <v>40726</v>
       </c>
@@ -5535,7 +5557,7 @@
         <v>6.87</v>
       </c>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="13">
         <v>40756</v>
       </c>
@@ -5552,7 +5574,7 @@
         <v>7.23</v>
       </c>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="13">
         <v>40787</v>
       </c>
@@ -5569,7 +5591,7 @@
         <v>7.31</v>
       </c>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="13">
         <v>40817</v>
       </c>
@@ -5586,7 +5608,7 @@
         <v>6.97</v>
       </c>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="13">
         <v>40848</v>
       </c>
@@ -5603,7 +5625,7 @@
         <v>6.64</v>
       </c>
     </row>
-    <row r="49" spans="1:5">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="9">
         <v>40878</v>
       </c>
@@ -5620,7 +5642,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="50" spans="1:5">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="19">
         <v>40909</v>
       </c>
@@ -5637,7 +5659,7 @@
         <v>6.22</v>
       </c>
     </row>
-    <row r="51" spans="1:5">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="13">
         <v>40940</v>
       </c>
@@ -5654,7 +5676,7 @@
         <v>5.85</v>
       </c>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="13">
         <v>40969</v>
       </c>
@@ -5671,7 +5693,7 @@
         <v>5.24</v>
       </c>
     </row>
-    <row r="53" spans="1:5">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="13">
         <v>41000</v>
       </c>
@@ -5688,7 +5710,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="43">
         <v>41030</v>
       </c>
@@ -5705,7 +5727,7 @@
         <v>4.99</v>
       </c>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="13">
         <v>41061</v>
       </c>
@@ -5722,7 +5744,7 @@
         <v>4.92</v>
       </c>
     </row>
-    <row r="56" spans="1:5">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="13">
         <v>41091</v>
       </c>
@@ -5739,7 +5761,7 @@
         <v>5.2</v>
       </c>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="13">
         <v>41122</v>
       </c>
@@ -5756,7 +5778,7 @@
         <v>5.24</v>
       </c>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="13">
         <v>41153</v>
       </c>
@@ -5773,7 +5795,7 @@
         <v>5.28</v>
       </c>
     </row>
-    <row r="59" spans="1:5">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="13">
         <v>41183</v>
       </c>
@@ -5790,7 +5812,7 @@
         <v>5.45</v>
       </c>
     </row>
-    <row r="60" spans="1:5">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="13">
         <v>41214</v>
       </c>
@@ -5807,7 +5829,7 @@
         <v>5.53</v>
       </c>
     </row>
-    <row r="61" spans="1:5">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="9">
         <v>41244</v>
       </c>
@@ -5824,7 +5846,7 @@
         <v>5.84</v>
       </c>
     </row>
-    <row r="62" spans="1:5">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>41275</v>
       </c>
@@ -5841,7 +5863,7 @@
         <v>6.15</v>
       </c>
     </row>
-    <row r="63" spans="1:5">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="13">
         <v>41306</v>
       </c>
@@ -5858,7 +5880,7 @@
         <v>6.31</v>
       </c>
     </row>
-    <row r="64" spans="1:5">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="13">
         <v>41334</v>
       </c>
@@ -5875,7 +5897,7 @@
         <v>6.59</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="13">
         <v>41365</v>
       </c>
@@ -5892,7 +5914,7 @@
         <v>6.49</v>
       </c>
     </row>
-    <row r="66" spans="1:5">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="13">
         <v>41395</v>
       </c>
@@ -5909,7 +5931,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="13">
         <v>41426</v>
       </c>
@@ -5926,7 +5948,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="13">
         <v>41456</v>
       </c>
@@ -5943,7 +5965,7 @@
         <v>6.27</v>
       </c>
     </row>
-    <row r="69" spans="1:5">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="13">
         <v>41487</v>
       </c>
@@ -5960,7 +5982,7 @@
         <v>6.09</v>
       </c>
     </row>
-    <row r="70" spans="1:5">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="13">
         <v>41518</v>
       </c>
@@ -5977,7 +5999,7 @@
         <v>5.86</v>
       </c>
     </row>
-    <row r="71" spans="1:5">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="13">
         <v>41548</v>
       </c>
@@ -5994,7 +6016,7 @@
         <v>5.84</v>
       </c>
     </row>
-    <row r="72" spans="1:5">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="13">
         <v>41579</v>
       </c>
@@ -6011,7 +6033,7 @@
         <v>5.77</v>
       </c>
     </row>
-    <row r="73" spans="1:5">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="9">
         <v>41609</v>
       </c>
@@ -6028,7 +6050,7 @@
         <v>5.91</v>
       </c>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="13">
         <v>41640</v>
       </c>
@@ -6045,7 +6067,7 @@
         <v>5.59</v>
       </c>
     </row>
-    <row r="75" spans="1:5">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="13">
         <v>41671</v>
       </c>
@@ -6062,7 +6084,7 @@
         <v>5.68</v>
       </c>
     </row>
-    <row r="76" spans="1:5">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="13">
         <v>41699</v>
       </c>
@@ -6079,7 +6101,7 @@
         <v>6.15</v>
       </c>
     </row>
-    <row r="77" spans="1:5">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="13">
         <v>41730</v>
       </c>
@@ -6096,7 +6118,7 @@
         <v>6.28</v>
       </c>
     </row>
-    <row r="78" spans="1:5">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="13">
         <v>41760</v>
       </c>
@@ -6113,7 +6135,7 @@
         <v>6.37</v>
       </c>
     </row>
-    <row r="79" spans="1:5">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="13">
         <v>41791</v>
       </c>
@@ -6130,7 +6152,7 @@
         <v>6.52</v>
       </c>
     </row>
-    <row r="80" spans="1:5">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="13">
         <v>41821</v>
       </c>
@@ -6147,7 +6169,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="81" spans="1:5">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="13">
         <v>41852</v>
       </c>
@@ -6164,7 +6186,7 @@
         <v>6.51</v>
       </c>
     </row>
-    <row r="82" spans="1:5">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="13">
         <v>41883</v>
       </c>
@@ -6181,7 +6203,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="83" spans="1:5">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="13">
         <v>41913</v>
       </c>
@@ -6198,7 +6220,7 @@
         <v>6.59</v>
       </c>
     </row>
-    <row r="84" spans="1:5">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="13">
         <v>41944</v>
       </c>
@@ -6215,7 +6237,7 @@
         <v>6.56</v>
       </c>
     </row>
-    <row r="85" spans="1:5">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="9">
         <v>41974</v>
       </c>
@@ -6232,7 +6254,7 @@
         <v>6.41</v>
       </c>
     </row>
-    <row r="86" spans="1:5">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="19">
         <v>42005</v>
       </c>
@@ -6249,7 +6271,7 @@
         <v>7.14</v>
       </c>
     </row>
-    <row r="87" spans="1:5">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="13">
         <v>42036</v>
       </c>
@@ -6266,7 +6288,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="88" spans="1:5">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="13">
         <v>42064</v>
       </c>
@@ -6283,7 +6305,7 @@
         <v>8.1300000000000008</v>
       </c>
     </row>
-    <row r="89" spans="1:5">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="13">
         <v>42095</v>
       </c>
@@ -6300,7 +6322,7 @@
         <v>8.17</v>
       </c>
     </row>
-    <row r="90" spans="1:5">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="13">
         <v>42125</v>
       </c>
@@ -6317,7 +6339,7 @@
         <v>8.4700000000000006</v>
       </c>
     </row>
-    <row r="91" spans="1:5">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="13">
         <v>42156</v>
       </c>
@@ -6334,7 +6356,7 @@
         <v>8.89</v>
       </c>
     </row>
-    <row r="92" spans="1:5">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="13">
         <v>42186</v>
       </c>
@@ -6351,7 +6373,7 @@
         <v>9.56</v>
       </c>
     </row>
-    <row r="93" spans="1:5">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="13">
         <v>42217</v>
       </c>
@@ -6368,7 +6390,7 @@
         <v>9.5299999999999994</v>
       </c>
     </row>
-    <row r="94" spans="1:5">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="13">
         <v>42248</v>
       </c>
@@ -6385,7 +6407,7 @@
         <v>9.49</v>
       </c>
     </row>
-    <row r="95" spans="1:5">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="13">
         <v>42278</v>
       </c>
@@ -6402,7 +6424,7 @@
         <v>9.93</v>
       </c>
     </row>
-    <row r="96" spans="1:5">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="13">
         <v>42309</v>
       </c>
@@ -6419,7 +6441,7 @@
         <v>10.48</v>
       </c>
     </row>
-    <row r="97" spans="1:5">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="9">
         <v>42339</v>
       </c>
@@ -6436,7 +6458,7 @@
         <v>10.67</v>
       </c>
     </row>
-    <row r="98" spans="1:5">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="13">
         <v>42370</v>
       </c>
@@ -6453,7 +6475,7 @@
         <v>10.71</v>
       </c>
     </row>
-    <row r="99" spans="1:5">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="13">
         <v>42401</v>
       </c>
@@ -6470,7 +6492,7 @@
         <v>10.36</v>
       </c>
     </row>
-    <row r="100" spans="1:5">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="13">
         <v>42430</v>
       </c>
@@ -6487,7 +6509,7 @@
         <v>9.39</v>
       </c>
     </row>
-    <row r="101" spans="1:5">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="13">
         <v>42461</v>
       </c>
@@ -6504,7 +6526,7 @@
         <v>9.2799999999999994</v>
       </c>
     </row>
-    <row r="102" spans="1:5">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="13">
         <v>42491</v>
       </c>
@@ -6521,7 +6543,7 @@
         <v>9.32</v>
       </c>
     </row>
-    <row r="103" spans="1:5">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="13">
         <v>42522</v>
       </c>
@@ -6538,7 +6560,7 @@
         <v>8.84</v>
       </c>
     </row>
-    <row r="104" spans="1:5">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="13">
         <v>42552</v>
       </c>
@@ -6555,7 +6577,7 @@
         <v>8.74</v>
       </c>
     </row>
-    <row r="105" spans="1:5">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="13">
         <v>42583</v>
       </c>
@@ -6572,7 +6594,7 @@
         <v>8.9700000000000006</v>
       </c>
     </row>
-    <row r="106" spans="1:5">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="13">
         <v>42614</v>
       </c>
@@ -6589,7 +6611,7 @@
         <v>8.48</v>
       </c>
     </row>
-    <row r="107" spans="1:5">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="13">
         <v>42644</v>
       </c>
@@ -6606,7 +6628,7 @@
         <v>7.87</v>
       </c>
     </row>
-    <row r="108" spans="1:5">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="13">
         <v>42675</v>
       </c>
@@ -6623,7 +6645,7 @@
         <v>6.99</v>
       </c>
     </row>
-    <row r="109" spans="1:5">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="9">
         <v>42705</v>
       </c>
@@ -6640,7 +6662,7 @@
         <v>6.29</v>
       </c>
     </row>
-    <row r="110" spans="1:5">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="13">
         <v>42736</v>
       </c>
@@ -6657,7 +6679,7 @@
         <v>5.35</v>
       </c>
     </row>
-    <row r="111" spans="1:5">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="13">
         <v>42767</v>
       </c>
@@ -6674,7 +6696,7 @@
         <v>4.76</v>
       </c>
     </row>
-    <row r="112" spans="1:5">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="13">
         <v>42795</v>
       </c>
@@ -6691,7 +6713,7 @@
         <v>4.57</v>
       </c>
     </row>
-    <row r="113" spans="1:5">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="13">
         <v>42826</v>
       </c>
@@ -6708,7 +6730,7 @@
         <v>4.08</v>
       </c>
     </row>
-    <row r="114" spans="1:5">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="13">
         <v>42856</v>
       </c>
@@ -6725,7 +6747,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="115" spans="1:5">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="13">
         <v>42887</v>
       </c>
@@ -6742,7 +6764,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="116" spans="1:5">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="13">
         <v>42917</v>
       </c>
@@ -6759,7 +6781,7 @@
         <v>2.71</v>
       </c>
     </row>
-    <row r="117" spans="1:5">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="13">
         <v>42948</v>
       </c>
@@ -6776,7 +6798,7 @@
         <v>2.46</v>
       </c>
     </row>
-    <row r="118" spans="1:5">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="13">
         <v>42979</v>
       </c>
@@ -6793,7 +6815,7 @@
         <v>2.54</v>
       </c>
     </row>
-    <row r="119" spans="1:5">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="13">
         <v>43009</v>
       </c>
@@ -6810,7 +6832,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="120" spans="1:5">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="13">
         <v>43040</v>
       </c>
@@ -6827,7 +6849,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="121" spans="1:5">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="9">
         <v>43070</v>
       </c>
@@ -6844,7 +6866,7 @@
         <v>2.95</v>
       </c>
     </row>
-    <row r="122" spans="1:5">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>43101</v>
       </c>
@@ -6861,7 +6883,7 @@
         <v>2.86</v>
       </c>
     </row>
-    <row r="123" spans="1:5">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="5">
         <v>43132</v>
       </c>
@@ -6878,7 +6900,7 @@
         <v>2.84</v>
       </c>
     </row>
-    <row r="124" spans="1:5">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="5">
         <v>43160</v>
       </c>
@@ -6895,7 +6917,7 @@
         <v>2.68</v>
       </c>
     </row>
-    <row r="125" spans="1:5">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="5">
         <v>43191</v>
       </c>
@@ -6912,7 +6934,7 @@
         <v>2.76</v>
       </c>
     </row>
-    <row r="126" spans="1:5">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="5">
         <v>43221</v>
       </c>
@@ -6929,7 +6951,7 @@
         <v>2.86</v>
       </c>
     </row>
-    <row r="127" spans="1:5">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="5">
         <v>43252</v>
       </c>
@@ -6946,7 +6968,7 @@
         <v>4.3899999999999997</v>
       </c>
     </row>
-    <row r="128" spans="1:5">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="13">
         <v>43282</v>
       </c>
@@ -6963,7 +6985,7 @@
         <v>4.4800000000000004</v>
       </c>
     </row>
-    <row r="129" spans="1:5">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="13">
         <v>43313</v>
       </c>
@@ -6980,7 +7002,7 @@
         <v>4.1900000000000004</v>
       </c>
     </row>
-    <row r="130" spans="1:5">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="13">
         <v>43344</v>
       </c>
@@ -6997,7 +7019,7 @@
         <v>4.53</v>
       </c>
     </row>
-    <row r="131" spans="1:5">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" s="13">
         <v>43374</v>
       </c>
@@ -7014,7 +7036,7 @@
         <v>4.5599999999999996</v>
       </c>
     </row>
-    <row r="132" spans="1:5">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="13">
         <v>43405</v>
       </c>
@@ -7031,7 +7053,7 @@
         <v>4.05</v>
       </c>
     </row>
-    <row r="133" spans="1:5">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" s="9">
         <v>43435</v>
       </c>
@@ -7048,7 +7070,7 @@
         <v>3.75</v>
       </c>
     </row>
-    <row r="134" spans="1:5">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="19">
         <v>43466</v>
       </c>
@@ -7065,7 +7087,7 @@
         <v>3.78</v>
       </c>
     </row>
-    <row r="135" spans="1:5">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="13">
         <v>43497</v>
       </c>
@@ -7082,7 +7104,7 @@
         <v>3.89</v>
       </c>
     </row>
-    <row r="136" spans="1:5">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" s="13">
         <v>43525</v>
       </c>
@@ -7099,7 +7121,7 @@
         <v>4.58</v>
       </c>
     </row>
-    <row r="137" spans="1:5">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" s="13">
         <v>43556</v>
       </c>
@@ -7116,7 +7138,7 @@
         <v>4.9400000000000004</v>
       </c>
     </row>
-    <row r="138" spans="1:5">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" s="13">
         <v>43586</v>
       </c>
@@ -7133,7 +7155,7 @@
         <v>4.66</v>
       </c>
     </row>
-    <row r="139" spans="1:5">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" s="13">
         <v>43617</v>
       </c>
@@ -7150,7 +7172,7 @@
         <v>3.37</v>
       </c>
     </row>
-    <row r="140" spans="1:5">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" s="13">
         <v>43647</v>
       </c>
@@ -7167,7 +7189,7 @@
         <v>3.22</v>
       </c>
     </row>
-    <row r="141" spans="1:5">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" s="13">
         <v>43678</v>
       </c>
@@ -7184,7 +7206,7 @@
         <v>3.43</v>
       </c>
     </row>
-    <row r="142" spans="1:5">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" s="13">
         <v>43709</v>
       </c>
@@ -7201,7 +7223,7 @@
         <v>2.89</v>
       </c>
     </row>
-    <row r="143" spans="1:5">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" s="13">
         <v>43739</v>
       </c>
@@ -7218,7 +7240,7 @@
         <v>2.54</v>
       </c>
     </row>
-    <row r="144" spans="1:5">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" s="13">
         <v>43770</v>
       </c>
@@ -7235,7 +7257,7 @@
         <v>3.27</v>
       </c>
     </row>
-    <row r="145" spans="1:5">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" s="9">
         <v>43800</v>
       </c>
@@ -7252,7 +7274,7 @@
         <v>4.3099999999999996</v>
       </c>
     </row>
-    <row r="146" spans="1:5">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" s="19">
         <v>43831</v>
       </c>
@@ -7269,7 +7291,7 @@
         <v>4.1900000000000004</v>
       </c>
     </row>
-    <row r="147" spans="1:5">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" s="13">
         <v>43862</v>
       </c>
@@ -7286,7 +7308,7 @@
         <v>4.01</v>
       </c>
     </row>
-    <row r="148" spans="1:5">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" s="13">
         <v>43891</v>
       </c>
@@ -7303,7 +7325,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="149" spans="1:5">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" s="13">
         <v>43922</v>
       </c>
@@ -7320,7 +7342,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="150" spans="1:5">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" s="13">
         <v>43952</v>
       </c>
@@ -7337,7 +7359,7 @@
         <v>1.88</v>
       </c>
     </row>
-    <row r="151" spans="1:5">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" s="13">
         <v>43983</v>
       </c>
@@ -7354,7 +7376,7 @@
         <v>2.13</v>
       </c>
     </row>
-    <row r="152" spans="1:5">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" s="13">
         <v>44013</v>
       </c>
@@ -7371,7 +7393,7 @@
         <v>2.31</v>
       </c>
     </row>
-    <row r="153" spans="1:5">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" s="13">
         <v>44044</v>
       </c>
@@ -7388,7 +7410,7 @@
         <v>2.44</v>
       </c>
     </row>
-    <row r="154" spans="1:5">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" s="13">
         <v>44075</v>
       </c>
@@ -7405,7 +7427,7 @@
         <v>3.14</v>
       </c>
     </row>
-    <row r="155" spans="1:5">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" s="13">
         <v>44105</v>
       </c>
@@ -7422,7 +7444,7 @@
         <v>3.92</v>
       </c>
     </row>
-    <row r="156" spans="1:5">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" s="13">
         <v>44136</v>
       </c>
@@ -7439,7 +7461,7 @@
         <v>4.3099999999999996</v>
       </c>
     </row>
-    <row r="157" spans="1:5">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" s="9">
         <v>44166</v>
       </c>
@@ -7456,7 +7478,7 @@
         <v>4.5199999999999996</v>
       </c>
     </row>
-    <row r="158" spans="1:5">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" s="13">
         <v>44197</v>
       </c>
@@ -7473,7 +7495,7 @@
         <v>4.5599999999999996</v>
       </c>
     </row>
-    <row r="159" spans="1:5">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" s="13">
         <v>44228</v>
       </c>
@@ -7490,7 +7512,7 @@
         <v>5.2</v>
       </c>
     </row>
-    <row r="160" spans="1:5">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" s="13">
         <v>44256</v>
       </c>
@@ -7507,7 +7529,7 @@
         <v>6.1</v>
       </c>
     </row>
-    <row r="161" spans="1:5">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" s="13">
         <v>44287</v>
       </c>
@@ -7524,7 +7546,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="162" spans="1:5">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" s="13">
         <v>44317</v>
       </c>
@@ -7541,7 +7563,7 @@
         <v>8.06</v>
       </c>
     </row>
-    <row r="163" spans="1:5">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" s="13">
         <v>44348</v>
       </c>
@@ -7558,7 +7580,7 @@
         <v>8.35</v>
       </c>
     </row>
-    <row r="164" spans="1:5">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" s="13">
         <v>44378</v>
       </c>
@@ -7575,7 +7597,7 @@
         <v>8.99</v>
       </c>
     </row>
-    <row r="165" spans="1:5">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" s="13">
         <v>44409</v>
       </c>
@@ -7592,7 +7614,7 @@
         <v>9.68</v>
       </c>
     </row>
-    <row r="166" spans="1:5">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" s="13">
         <v>44440</v>
       </c>
@@ -7609,7 +7631,7 @@
         <v>10.25</v>
       </c>
     </row>
-    <row r="167" spans="1:5">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" s="13">
         <v>44470</v>
       </c>
@@ -7626,7 +7648,7 @@
         <v>10.67</v>
       </c>
     </row>
-    <row r="168" spans="1:5">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" s="13">
         <v>44501</v>
       </c>
@@ -7643,7 +7665,7 @@
         <v>10.74</v>
       </c>
     </row>
-    <row r="169" spans="1:5">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" s="9">
         <v>44531</v>
       </c>
@@ -7660,7 +7682,7 @@
         <v>10.06</v>
       </c>
     </row>
-    <row r="170" spans="1:5">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" s="13">
         <v>44562</v>
       </c>
@@ -7677,7 +7699,7 @@
         <v>10.38</v>
       </c>
     </row>
-    <row r="171" spans="1:5">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" s="13">
         <v>44593</v>
       </c>
@@ -7694,7 +7716,7 @@
         <v>10.54</v>
       </c>
     </row>
-    <row r="172" spans="1:5">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" s="13">
         <v>44621</v>
       </c>
@@ -7711,7 +7733,7 @@
         <v>11.3</v>
       </c>
     </row>
-    <row r="173" spans="1:5">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" s="13">
         <v>44652</v>
       </c>
@@ -7728,7 +7750,7 @@
         <v>12.13</v>
       </c>
     </row>
-    <row r="174" spans="1:5">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" s="13">
         <v>44682</v>
       </c>
@@ -7745,7 +7767,7 @@
         <v>11.73</v>
       </c>
     </row>
-    <row r="175" spans="1:5">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" s="13">
         <v>44713</v>
       </c>
@@ -7762,7 +7784,7 @@
         <v>11.89</v>
       </c>
     </row>
-    <row r="176" spans="1:5">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" s="13">
         <v>44743</v>
       </c>
@@ -7779,7 +7801,7 @@
         <v>10.07</v>
       </c>
     </row>
-    <row r="177" spans="1:5">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" s="13">
         <v>44774</v>
       </c>
@@ -7796,7 +7818,7 @@
         <v>8.73</v>
       </c>
     </row>
-    <row r="178" spans="1:5">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" s="23">
         <v>44805</v>
       </c>
@@ -7813,7 +7835,7 @@
         <v>7.17</v>
       </c>
     </row>
-    <row r="179" spans="1:5">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" s="23">
         <v>44835</v>
       </c>
@@ -7830,7 +7852,7 @@
         <v>6.47</v>
       </c>
     </row>
-    <row r="180" spans="1:5">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" s="13">
         <v>44866</v>
       </c>
@@ -7847,7 +7869,7 @@
         <v>5.9</v>
       </c>
     </row>
-    <row r="181" spans="1:5">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" s="9">
         <v>44896</v>
       </c>
@@ -7864,7 +7886,7 @@
         <v>5.79</v>
       </c>
     </row>
-    <row r="182" spans="1:5">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" s="1">
         <v>44927</v>
       </c>
@@ -7881,7 +7903,7 @@
         <v>5.77</v>
       </c>
     </row>
-    <row r="183" spans="1:5">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" s="5">
         <v>44958</v>
       </c>
@@ -7898,7 +7920,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="184" spans="1:5">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" s="5">
         <v>44986</v>
       </c>
@@ -7915,7 +7937,7 @@
         <v>4.6500000000000004</v>
       </c>
     </row>
-    <row r="185" spans="1:5">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" s="5">
         <v>45017</v>
       </c>
@@ -7932,7 +7954,7 @@
         <v>4.18</v>
       </c>
     </row>
-    <row r="186" spans="1:5">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" s="5">
         <v>45047</v>
       </c>
@@ -7949,7 +7971,7 @@
         <v>3.94</v>
       </c>
     </row>
-    <row r="187" spans="1:5">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" s="5">
         <v>45078</v>
       </c>
@@ -7966,7 +7988,7 @@
         <v>3.16</v>
       </c>
     </row>
-    <row r="188" spans="1:5">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" s="5">
         <v>45108</v>
       </c>
@@ -7983,7 +8005,7 @@
         <v>3.99</v>
       </c>
     </row>
-    <row r="189" spans="1:5">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" s="5">
         <v>45139</v>
       </c>
@@ -8000,7 +8022,7 @@
         <v>4.6100000000000003</v>
       </c>
     </row>
-    <row r="190" spans="1:5">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" s="5">
         <v>45170</v>
       </c>
@@ -8017,7 +8039,7 @@
         <v>5.19</v>
       </c>
     </row>
-    <row r="191" spans="1:5">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" s="5">
         <v>45200</v>
       </c>
@@ -8034,7 +8056,7 @@
         <v>4.82</v>
       </c>
     </row>
-    <row r="192" spans="1:5">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" s="5">
         <v>45231</v>
       </c>
@@ -8051,7 +8073,7 @@
         <v>4.68</v>
       </c>
     </row>
-    <row r="193" spans="1:5">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" s="13">
         <v>45261</v>
       </c>
@@ -8068,7 +8090,7 @@
         <v>4.62</v>
       </c>
     </row>
-    <row r="194" spans="1:5">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" s="48">
         <v>45292</v>
       </c>
@@ -8085,7 +8107,7 @@
         <v>4.51</v>
       </c>
     </row>
-    <row r="195" spans="1:5">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" s="31">
         <v>45323</v>
       </c>
@@ -8102,7 +8124,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="196" spans="1:5">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" s="31">
         <v>45352</v>
       </c>
@@ -8119,7 +8141,7 @@
         <v>3.93</v>
       </c>
     </row>
-    <row r="197" spans="1:5">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197" s="31">
         <v>45383</v>
       </c>
@@ -8136,7 +8158,7 @@
         <v>3.69</v>
       </c>
     </row>
-    <row r="198" spans="1:5">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" s="31">
         <v>45413</v>
       </c>
@@ -8153,7 +8175,7 @@
         <v>3.93</v>
       </c>
     </row>
-    <row r="199" spans="1:5">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A199" s="31">
         <v>45444</v>
       </c>
@@ -8170,7 +8192,7 @@
         <v>4.2300000000000004</v>
       </c>
     </row>
-    <row r="200" spans="1:5">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200" s="31">
         <v>45474</v>
       </c>
@@ -8187,7 +8209,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="201" spans="1:5">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201" s="31">
         <v>45505</v>
       </c>
@@ -8204,7 +8226,7 @@
         <v>4.24</v>
       </c>
     </row>
-    <row r="202" spans="1:5">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A202" s="31">
         <v>45536</v>
       </c>
@@ -8221,7 +8243,7 @@
         <v>4.42</v>
       </c>
     </row>
-    <row r="203" spans="1:5">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A203" s="31">
         <v>45566</v>
       </c>
@@ -8238,7 +8260,7 @@
         <v>4.76</v>
       </c>
     </row>
-    <row r="204" spans="1:5">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A204" s="31">
         <v>45597</v>
       </c>
@@ -8255,7 +8277,7 @@
         <v>4.87</v>
       </c>
     </row>
-    <row r="205" spans="1:5">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A205" s="27">
         <v>45627</v>
       </c>
@@ -8272,7 +8294,7 @@
         <v>4.83</v>
       </c>
     </row>
-    <row r="206" spans="1:5">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A206" s="23">
         <v>45658</v>
       </c>
@@ -8289,7 +8311,7 @@
         <v>4.5599999999999996</v>
       </c>
     </row>
-    <row r="207" spans="1:5">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A207" s="31">
         <v>45689</v>
       </c>
@@ -8306,7 +8328,7 @@
         <v>5.0599999999999996</v>
       </c>
     </row>
-    <row r="208" spans="1:5">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A208" s="31">
         <v>45717</v>
       </c>
@@ -8323,7 +8345,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="209" spans="1:5">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A209" s="31">
         <v>45748</v>
       </c>
@@ -8340,7 +8362,7 @@
         <v>5.53</v>
       </c>
     </row>
-    <row r="210" spans="1:5">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A210" s="31">
         <v>45778</v>
       </c>
@@ -8357,7 +8379,7 @@
         <v>5.32</v>
       </c>
     </row>
-    <row r="211" spans="1:5">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A211" s="23">
         <v>45809</v>
       </c>
@@ -8374,7 +8396,7 @@
         <v>5.35</v>
       </c>
     </row>
-    <row r="212" spans="1:5">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A212" s="23">
         <v>45839</v>
       </c>
@@ -8391,7 +8413,7 @@
         <v>5.23</v>
       </c>
     </row>
-    <row r="213" spans="1:5">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213" s="23">
         <v>45870</v>
       </c>
@@ -8408,7 +8430,7 @@
         <v>5.13</v>
       </c>
     </row>
-    <row r="214" spans="1:5">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A214" s="23">
         <v>45901</v>
       </c>
@@ -8425,7 +8447,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="215" spans="1:5">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A215" s="23">
         <v>45931</v>
       </c>
@@ -8442,7 +8464,7 @@
         <v>4.68</v>
       </c>
     </row>
-    <row r="216" spans="1:5">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A216" s="23">
         <v>45962</v>
       </c>
@@ -8459,7 +8481,7 @@
         <v>4.46</v>
       </c>
     </row>
-    <row r="217" spans="1:5">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A217" s="27">
         <v>45992</v>
       </c>
@@ -8476,7 +8498,7 @@
         <v>4.26</v>
       </c>
     </row>
-    <row r="218" spans="1:5">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A218" s="19">
         <v>46023</v>
       </c>
@@ -8493,7 +8515,7 @@
         <v>4.4400000000000004</v>
       </c>
     </row>
-    <row r="219" spans="1:5">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A219" s="23">
         <v>46054</v>
       </c>
@@ -8510,7 +8532,7 @@
         <v>3.81</v>
       </c>
     </row>
-    <row r="220" spans="1:5">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A220" s="23">
         <v>46082</v>
       </c>
@@ -8527,7 +8549,7 @@
         <v>4.1399999999999997</v>
       </c>
     </row>
-    <row r="221" spans="1:5">
+    <row r="221" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A221" s="9">
         <v>46114</v>
       </c>
@@ -8542,6 +8564,23 @@
       </c>
       <c r="E221" s="12">
         <v>4.3899999999999997</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A222" s="19">
+        <v>46143</v>
+      </c>
+      <c r="B222" s="47">
+        <v>7640.15</v>
+      </c>
+      <c r="C222" s="25">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="D222" s="25">
+        <v>3.2</v>
+      </c>
+      <c r="E222" s="26">
+        <v>4.72</v>
       </c>
     </row>
   </sheetData>
